--- a/docs/sales-reform-toolkit/sto/STO週次運用管理.xlsx
+++ b/docs/sales-reform-toolkit/sto/STO週次運用管理.xlsx
@@ -2029,7 +2029,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B2:B21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"坪井,岡田,新谷,柳沼"</formula1>
+      <formula1>"新谷,小澤,坪井,大塩,柳沼"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>坪井</t>
+          <t>小澤</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>岡田</t>
+          <t>坪井</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>柳沼</t>
+          <t>大塩</t>
         </is>
       </c>
     </row>
@@ -2564,6 +2564,11 @@
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t>点検会議</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>柳沼</t>
         </is>
       </c>
     </row>

--- a/docs/sales-reform-toolkit/sto/STO週次運用管理.xlsx
+++ b/docs/sales-reform-toolkit/sto/STO週次運用管理.xlsx
@@ -595,7 +595,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>・週次レビューは毎週金曜17:00の30分。新谷・坪井・岡田で実施。画面共有のみで運用し、別途資料は作らない。</t>
+          <t>・週次レビューは毎週金曜17:00の30分。新谷・小澤・坪井で実施。画面共有のみで運用し、別途資料は作らない。</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2052,6 +2052,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2081,25 +2082,30 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>坪井さん</t>
+          <t>小澤</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>岡田さん</t>
+          <t>坪井</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>柳沼さん</t>
+          <t>大塩</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
+          <t>柳沼</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
           <t>各部長</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>分科会リーダー</t>
         </is>
@@ -2116,15 +2122,16 @@
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr"/>
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr"/>
       <c r="E5" s="10" t="inlineStr"/>
       <c r="F5" s="10" t="inlineStr"/>
       <c r="G5" s="10" t="inlineStr"/>
+      <c r="H5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -2137,19 +2144,20 @@
           <t>A</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr"/>
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr"/>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr"/>
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr"/>
       <c r="G6" s="10" t="inlineStr"/>
+      <c r="H6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -2162,19 +2170,20 @@
           <t>I</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr"/>
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr"/>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr"/>
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr"/>
       <c r="G7" s="10" t="inlineStr"/>
+      <c r="H7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -2187,19 +2196,20 @@
           <t>A</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr"/>
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr"/>
       <c r="E8" s="10" t="inlineStr"/>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr"/>
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -2218,7 +2228,7 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
@@ -2228,7 +2238,12 @@
           <t>R</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -2245,19 +2260,28 @@
           <t>A</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr"/>
-      <c r="E10" s="10" t="inlineStr"/>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr"/>
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -2275,20 +2299,21 @@
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr"/>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr"/>
+      <c r="F11" s="10" t="inlineStr"/>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
         <is>
           <t>R</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr"/>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>C</t>
         </is>
       </c>
     </row>
@@ -2298,9 +2323,9 @@
           <t>議事録・宿題起票</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr"/>
@@ -2311,7 +2336,8 @@
       </c>
       <c r="E12" s="10" t="inlineStr"/>
       <c r="F12" s="10" t="inlineStr"/>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr"/>
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -2335,12 +2361,13 @@
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr"/>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr"/>
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -2368,12 +2395,13 @@
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr"/>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr"/>
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -2402,7 +2430,8 @@
       </c>
       <c r="E15" s="10" t="inlineStr"/>
       <c r="F15" s="10" t="inlineStr"/>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr"/>
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -2419,19 +2448,16 @@
           <t>R/A</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr"/>
+      <c r="C16" s="10" t="inlineStr"/>
+      <c r="D16" s="10" t="inlineStr"/>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="F16" s="10" t="inlineStr"/>
       <c r="G16" s="10" t="inlineStr"/>
+      <c r="H16" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/sales-reform-toolkit/sto/STO週次運用管理.xlsx
+++ b/docs/sales-reform-toolkit/sto/STO週次運用管理.xlsx
@@ -595,7 +595,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>・週次レビューは毎週金曜17:00の30分。新谷・小澤・坪井で実施。画面共有のみで運用し、別途資料は作らない。</t>
+          <t>・週次レビューは毎週金曜17:00の30分。新谷・小沢・坪井で実施。画面共有のみで運用し、別途資料は作らない。</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B2:B21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"新谷,小澤,坪井,大塩,柳沼"</formula1>
+      <formula1>"新谷,小沢,坪井,大塩,柳沼"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>小澤</t>
+          <t>小沢</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>小澤</t>
+          <t>小沢</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
